--- a/data/quotas/quota_onnuri_2026_풍납시장_온누리가맹점_조사쿼터_1791810614874.xlsx
+++ b/data/quotas/quota_onnuri_2026_풍납시장_온누리가맹점_조사쿼터_1791810614874.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:N21"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -405,12 +405,14 @@
     <col min="4" max="4" width="19.234375" customWidth="1"/>
     <col min="5" max="5" width="12.6328125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="48.83203125" customWidth="1"/>
-    <col min="9" max="9" width="56.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="17.03515625" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="48.83203125" customWidth="1"/>
+    <col min="11" max="11" width="56.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="17.03515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -430,24 +432,30 @@
         <v>대표자명</v>
       </c>
       <c r="F1" t="str">
+        <v>성별</v>
+      </c>
+      <c r="G1" t="str">
+        <v>나이</v>
+      </c>
+      <c r="H1" t="str">
         <v>연락처</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>개업연월</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>취급품목</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>주소</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>가맹상태</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>온누리지류</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>온누리디지털</v>
       </c>
     </row>
@@ -471,21 +479,27 @@
         <v/>
       </c>
       <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
         <v>2020.10.06</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>수산물 (신선)</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>서울특별시 송파구 풍납동   1층</v>
       </c>
-      <c r="J2" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Y</v>
-      </c>
       <c r="L2" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N2" t="str">
         <v>N</v>
       </c>
     </row>
@@ -509,21 +523,27 @@
         <v/>
       </c>
       <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
         <v>2012.03.13</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>기타소매업 (두발 미용업)</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>서울특별시 송파구 풍납동 87-4 예작헤어라인</v>
       </c>
-      <c r="J3" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Y</v>
-      </c>
       <c r="L3" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N3" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -547,21 +567,27 @@
         <v/>
       </c>
       <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
         <v>2023.10.06</v>
       </c>
-      <c r="H4" t="str">
+      <c r="J4" t="str">
         <v>기타소매업 (피부 미용업)</v>
       </c>
-      <c r="I4" t="str">
+      <c r="K4" t="str">
         <v>서울특별시 송파구 풍납동 2층 201호</v>
       </c>
-      <c r="J4" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Y</v>
-      </c>
       <c r="L4" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N4" t="str">
         <v>N</v>
       </c>
     </row>
@@ -585,21 +611,27 @@
         <v/>
       </c>
       <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v>2025.06.11</v>
       </c>
-      <c r="H5" t="str">
+      <c r="J5" t="str">
         <v>농산물 (곡물)</v>
       </c>
-      <c r="I5" t="str">
+      <c r="K5" t="str">
         <v>서울특별시 송파구 풍납동 1층 4호</v>
       </c>
-      <c r="J5" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Y</v>
-      </c>
       <c r="L5" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N5" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -623,21 +655,27 @@
         <v/>
       </c>
       <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
         <v>2022.03.14</v>
       </c>
-      <c r="H6" t="str">
+      <c r="J6" t="str">
         <v>수산물 (음ㆍ식료품 및 담배 도매업 외 1개)</v>
       </c>
-      <c r="I6" t="str">
+      <c r="K6" t="str">
         <v>서울특별시 송파구 풍납동 149-12 1층</v>
       </c>
-      <c r="J6" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K6" t="str">
-        <v>Y</v>
-      </c>
       <c r="L6" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N6" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -661,21 +699,27 @@
         <v/>
       </c>
       <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
         <v>2011-05-12</v>
       </c>
-      <c r="H7" t="str">
+      <c r="J7" t="str">
         <v>가공식품</v>
       </c>
-      <c r="I7" t="str">
+      <c r="K7" t="str">
         <v>서울특별시 송파구 풍납동   1층</v>
       </c>
-      <c r="J7" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Y</v>
-      </c>
       <c r="L7" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N7" t="str">
         <v>N</v>
       </c>
     </row>
@@ -699,21 +743,27 @@
         <v/>
       </c>
       <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
         <v>2014.01.20</v>
       </c>
-      <c r="H8" t="str">
+      <c r="J8" t="str">
         <v>농산물 (육류 소매업)</v>
       </c>
-      <c r="I8" t="str">
+      <c r="K8" t="str">
         <v>서울특별시 송파구 풍납동 1층</v>
       </c>
-      <c r="J8" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Y</v>
-      </c>
       <c r="L8" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N8" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -737,21 +787,27 @@
         <v/>
       </c>
       <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
         <v>1991.04.03</v>
       </c>
-      <c r="H9" t="str">
+      <c r="J9" t="str">
         <v>농산물 (통신ㆍ방송장비 및 부품 도매업 외 1개)</v>
       </c>
-      <c r="I9" t="str">
+      <c r="K9" t="str">
         <v>서울특별시 송파구 풍납동   1층</v>
       </c>
-      <c r="J9" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K9" t="str">
-        <v>Y</v>
-      </c>
       <c r="L9" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N9" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -775,21 +831,27 @@
         <v/>
       </c>
       <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
         <v>2016.12.15</v>
       </c>
-      <c r="H10" t="str">
+      <c r="J10" t="str">
         <v>기타소매업 (음ㆍ식료품 및 담배 도매업 외 1개)</v>
       </c>
-      <c r="I10" t="str">
+      <c r="K10" t="str">
         <v>서울특별시 송파구 풍납동 477-3 1층</v>
       </c>
-      <c r="J10" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K10" t="str">
-        <v>Y</v>
-      </c>
       <c r="L10" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N10" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -813,21 +875,27 @@
         <v/>
       </c>
       <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
         <v>2010.06.16</v>
       </c>
-      <c r="H11" t="str">
+      <c r="J11" t="str">
         <v>음식점업 (한식 일반 음식점업 외 1개)</v>
       </c>
-      <c r="I11" t="str">
+      <c r="K11" t="str">
         <v>서울특별시 송파구 풍납동 478 1층 독도쭈꾸미</v>
       </c>
-      <c r="J11" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K11" t="str">
-        <v>Y</v>
-      </c>
       <c r="L11" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N11" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -851,21 +919,27 @@
         <v/>
       </c>
       <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
         <v>2026.07.13</v>
       </c>
-      <c r="H12" t="str">
+      <c r="J12" t="str">
         <v>기타소매업</v>
       </c>
-      <c r="I12" t="str">
+      <c r="K12" t="str">
         <v>서울특별시 송파구 풍납동 81-37 1층 103호</v>
       </c>
-      <c r="J12" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K12" t="str">
-        <v>Y</v>
-      </c>
       <c r="L12" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N12" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -889,21 +963,27 @@
         <v/>
       </c>
       <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
         <v>2026.04.07</v>
       </c>
-      <c r="H13" t="str">
+      <c r="J13" t="str">
         <v>음식점업</v>
       </c>
-      <c r="I13" t="str">
+      <c r="K13" t="str">
         <v>서울특별시 송파구 풍납동 78-83 1층 2호</v>
       </c>
-      <c r="J13" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K13" t="str">
-        <v>Y</v>
-      </c>
       <c r="L13" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N13" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -927,21 +1007,27 @@
         <v/>
       </c>
       <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
         <v>2025.08.25</v>
       </c>
-      <c r="H14" t="str">
+      <c r="J14" t="str">
         <v>기타소매업</v>
       </c>
-      <c r="I14" t="str">
+      <c r="K14" t="str">
         <v>서울특별시 송파구 풍납동 152-7 1층</v>
       </c>
-      <c r="J14" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K14" t="str">
-        <v>Y</v>
-      </c>
       <c r="L14" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N14" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -965,21 +1051,27 @@
         <v/>
       </c>
       <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
         <v>2026.05.15</v>
       </c>
-      <c r="H15" t="str">
+      <c r="J15" t="str">
         <v>음식점업</v>
       </c>
-      <c r="I15" t="str">
+      <c r="K15" t="str">
         <v>서울특별시 송파구 풍납동 81-37 1층 101호</v>
       </c>
-      <c r="J15" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K15" t="str">
-        <v>Y</v>
-      </c>
       <c r="L15" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N15" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -1003,21 +1095,27 @@
         <v/>
       </c>
       <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
         <v>2004.08.25</v>
       </c>
-      <c r="H16" t="str">
+      <c r="J16" t="str">
         <v>근린상권서비스 (병원 외 1개)</v>
       </c>
-      <c r="I16" t="str">
+      <c r="K16" t="str">
         <v>서울특별시 송파구 풍납동 152-28 백원빌딩 백원빌딩 2층</v>
       </c>
-      <c r="J16" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K16" t="str">
-        <v>Y</v>
-      </c>
       <c r="L16" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N16" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -1041,21 +1139,27 @@
         <v/>
       </c>
       <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
         <v>2026.02.05</v>
       </c>
-      <c r="H17" t="str">
+      <c r="J17" t="str">
         <v>음식점업 (기타 비알코올 음료점업)</v>
       </c>
-      <c r="I17" t="str">
+      <c r="K17" t="str">
         <v>서울특별시 송파구 풍납동 475-9 1층</v>
       </c>
-      <c r="J17" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K17" t="str">
-        <v>Y</v>
-      </c>
       <c r="L17" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N17" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -1079,21 +1183,27 @@
         <v/>
       </c>
       <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
         <v>2016.09.26</v>
       </c>
-      <c r="H18" t="str">
+      <c r="J18" t="str">
         <v>근린상권서비스 (두발 미용업)</v>
       </c>
-      <c r="I18" t="str">
+      <c r="K18" t="str">
         <v>서울특별시 송파구 풍납동 474-4 2층 리안헤어</v>
       </c>
-      <c r="J18" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K18" t="str">
-        <v>Y</v>
-      </c>
       <c r="L18" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N18" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -1117,21 +1227,27 @@
         <v/>
       </c>
       <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
         <v>2011-06-15</v>
       </c>
-      <c r="H19" t="str">
+      <c r="J19" t="str">
         <v>기타소매업</v>
       </c>
-      <c r="I19" t="str">
+      <c r="K19" t="str">
         <v>서울특별시 송파구 풍납동</v>
       </c>
-      <c r="J19" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K19" t="str">
-        <v>Y</v>
-      </c>
       <c r="L19" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N19" t="str">
         <v>N</v>
       </c>
     </row>
@@ -1155,21 +1271,27 @@
         <v/>
       </c>
       <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
         <v>2013.12.13</v>
       </c>
-      <c r="H20" t="str">
+      <c r="J20" t="str">
         <v>축산물 (육류 소매업)</v>
       </c>
-      <c r="I20" t="str">
+      <c r="K20" t="str">
         <v>서울특별시 송파구 풍납동   1층 2호</v>
       </c>
-      <c r="J20" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K20" t="str">
-        <v>Y</v>
-      </c>
       <c r="L20" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N20" t="str">
         <v>Y</v>
       </c>
     </row>
@@ -1193,27 +1315,33 @@
         <v/>
       </c>
       <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
         <v>2026-03-17</v>
       </c>
-      <c r="H21" t="str">
+      <c r="J21" t="str">
         <v>농산물</v>
       </c>
-      <c r="I21" t="str">
+      <c r="K21" t="str">
         <v>서울특별시 송파구 풍납동 149-12 -</v>
       </c>
-      <c r="J21" t="str">
-        <v>정상가맹</v>
-      </c>
-      <c r="K21" t="str">
-        <v>Y</v>
-      </c>
       <c r="L21" t="str">
+        <v>정상가맹</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N21" t="str">
         <v>N</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N21"/>
   </ignoredErrors>
 </worksheet>
 </file>